--- a/Result/profitability/3363.xlsx
+++ b/Result/profitability/3363.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.13875</v>
+        <v>-0.14875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.88875</v>
+        <v>13.1475</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01749999999999999</v>
+        <v>-0.007500000000000007</v>
       </c>
       <c r="N3" t="n">
-        <v>16.31875</v>
+        <v>15.1875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08625000000000002</v>
+        <v>0.0575</v>
       </c>
       <c r="N4" t="n">
-        <v>18.0325</v>
+        <v>15.9175</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10625</v>
+        <v>0.05875000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>15.605</v>
+        <v>13.16625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.125</v>
+        <v>0.0725</v>
       </c>
       <c r="N6" t="n">
-        <v>16.74625</v>
+        <v>13.79875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1267,7 +1267,7 @@
         <v>0.1575</v>
       </c>
       <c r="N7" t="n">
-        <v>16.03125</v>
+        <v>14.50625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2575</v>
+        <v>0.3525</v>
       </c>
       <c r="N8" t="n">
-        <v>18.07375</v>
+        <v>17.8675</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9449,6 +9449,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>429</v>
+      </c>
+      <c r="D72" t="n">
+        <v>428</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-92</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-21.43%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>64</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.18625</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12.335</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.7755102040816326</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>-0.8776595744680851</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-2.375</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-19.51</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>-0.9883485309017224</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
